--- a/NURBS IDX30 PYTHON ANALYSIS/Redo_front_4_24_26/15gps/2mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Redo_front_4_24_26/15gps/2mps_analysis.xlsx
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>396.2530044857585</v>
+        <v>396.4324107955624</v>
       </c>
       <c r="X3">
         <v>0.252648266</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>24.32323752768309</v>
+        <v>24.32189470780379</v>
       </c>
       <c r="X5">
         <v>0.252588824</v>
@@ -1987,7 +1987,7 @@
         <v>394.9316663034321</v>
       </c>
       <c r="V18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18">
         <v>0.252265552</v>
@@ -2073,7 +2073,7 @@
         <v>394.5708660154472</v>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19">
         <v>0.252257606</v>
@@ -2159,7 +2159,7 @@
         <v>394.2148833582001</v>
       </c>
       <c r="V20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20">
         <v>0.25223917</v>
@@ -2245,7 +2245,7 @@
         <v>393.9389435639923</v>
       </c>
       <c r="V21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21">
         <v>0.252224548</v>
